--- a/SGC-CKN/Excel/90e9179f-917a-4937-8331-98495f45d8c9_Lô_đất_ký_hiệu_CT-02_P11-87_D800_18-03-2026.xlsx
+++ b/SGC-CKN/Excel/90e9179f-917a-4937-8331-98495f45d8c9_Lô_đất_ký_hiệu_CT-02_P11-87_D800_18-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="65">
   <si>
     <t>Dự án</t>
   </si>
@@ -165,17 +165,21 @@
     <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ là hạt cát nhỏ, bụi</t>
   </si>
   <si>
+    <t xml:space="preserve">05:44
+18/03/2026</t>
+  </si>
+  <si>
+    <t>chạm sỏi</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
+  </si>
+  <si>
     <t xml:space="preserve">05:45
 18/03/2026</t>
-  </si>
-  <si>
-    <t>chạm sỏi</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">07:38
@@ -1367,13 +1371,13 @@
         <v>-44.5</v>
       </c>
       <c r="H17" s="25">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="I17" s="25">
         <v>6.1</v>
       </c>
       <c r="J17" s="12">
-        <v>8.13</v>
+        <v>8.32</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>49</v>
@@ -1390,10 +1394,10 @@
         <v>51</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F18" s="28">
         <v>-44.5</v>
@@ -1411,12 +1415,12 @@
         <v>2.78</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
@@ -1522,31 +1526,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1743,13 +1747,13 @@
         <v>-44.5</v>
       </c>
       <c r="G8" s="25">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="H8" s="25">
         <v>6.1</v>
       </c>
       <c r="I8" s="12">
-        <v>8.13</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1783,7 +1787,7 @@
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>30</v>
@@ -1801,13 +1805,13 @@
         <v>-49.74</v>
       </c>
       <c r="G10" s="33">
-        <v>6.3</v>
+        <v>6.28</v>
       </c>
       <c r="H10" s="33">
         <v>48.58</v>
       </c>
       <c r="I10" s="33">
-        <v>7.71</v>
+        <v>7.73</v>
       </c>
     </row>
   </sheetData>
